--- a/artfynd/A 4620-2024 artfynd.xlsx
+++ b/artfynd/A 4620-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440157</v>
       </c>
       <c r="B2" t="n">
-        <v>99330</v>
+        <v>99343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136440154</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4620-2024 artfynd.xlsx
+++ b/artfynd/A 4620-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440157</v>
       </c>
       <c r="B2" t="n">
-        <v>99343</v>
+        <v>99344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136440154</v>
       </c>
       <c r="B3" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4620-2024 artfynd.xlsx
+++ b/artfynd/A 4620-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Maria Magnusson, Emilia Fagerberg</t>
+          <t>Emilia Fagerberg, Maria Magnusson, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Maria Magnusson, Emilia Fagerberg</t>
+          <t>Emilia Fagerberg, Maria Magnusson, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
